--- a/Results/Study 1/ResNet50 (pretrained)/Confusion Matrices.xlsx
+++ b/Results/Study 1/ResNet50 (pretrained)/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>330</v>
+        <v>471</v>
       </c>
       <c r="C2">
-        <v>310</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="C3">
-        <v>479</v>
+        <v>537</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="C2">
-        <v>105</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
